--- a/tables/HWE_DEVIATIONS.xlsx
+++ b/tables/HWE_DEVIATIONS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\woodbison\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\Bison_github\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECCAA36-70DF-4082-AD53-7CF1BE0D7BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A5ED1E-1E1E-4BE5-9510-D241FA469EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15870" yWindow="-4080" windowWidth="15990" windowHeight="24720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -312,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -335,7 +335,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -629,126 +628,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE50"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="5.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.140625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="R1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="S1" s="12" t="s">
+      <c r="R1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="T1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="W1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="X1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Y1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="Z1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AA1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AB1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AC1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="AD1" s="12" t="s">
+      <c r="AD1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="AE1" s="12" t="s">
+      <c r="AE1" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
@@ -840,7 +843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
@@ -932,7 +935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
@@ -1024,7 +1027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
@@ -1116,7 +1119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
@@ -1208,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
@@ -1300,7 +1303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
@@ -1392,7 +1395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>21</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>24</v>
       </c>
@@ -1668,7 +1671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -1754,13 +1757,13 @@
         <v>1</v>
       </c>
       <c r="AD12" s="1">
-        <v>0.88319999999999999</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="AE12" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>26</v>
       </c>
@@ -1852,7 +1855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
@@ -1944,7 +1947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>28</v>
       </c>
@@ -2036,7 +2039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>29</v>
       </c>
@@ -2128,7 +2131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>30</v>
       </c>
@@ -2220,7 +2223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>31</v>
       </c>
@@ -2312,7 +2315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>32</v>
       </c>
@@ -2404,7 +2407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>33</v>
       </c>
@@ -2496,7 +2499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>34</v>
       </c>
@@ -2588,7 +2591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>35</v>
       </c>
@@ -2680,7 +2683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>36</v>
       </c>
@@ -2772,7 +2775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>38</v>
       </c>
@@ -2956,7 +2959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
@@ -3048,7 +3051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>40</v>
       </c>
@@ -3140,7 +3143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
@@ -3232,7 +3235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>42</v>
       </c>
@@ -3324,7 +3327,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>43</v>
       </c>
@@ -3416,7 +3419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>44</v>
       </c>
@@ -3508,7 +3511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>45</v>
       </c>
@@ -3600,7 +3603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>46</v>
       </c>
@@ -3692,7 +3695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>47</v>
       </c>
@@ -3784,7 +3787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>48</v>
       </c>
@@ -3876,7 +3879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>49</v>
       </c>
@@ -3968,7 +3971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>50</v>
       </c>
@@ -4060,7 +4063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>51</v>
       </c>
@@ -4152,7 +4155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>52</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>53</v>
       </c>
@@ -4336,7 +4339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>54</v>
       </c>
@@ -4428,7 +4431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>55</v>
       </c>
@@ -4520,7 +4523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>56</v>
       </c>
@@ -4612,7 +4615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>57</v>
       </c>
@@ -4704,7 +4707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>58</v>
       </c>
@@ -4796,7 +4799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>59</v>
       </c>
@@ -4888,7 +4891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>60</v>
       </c>
@@ -4980,7 +4983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>61</v>
       </c>
@@ -5072,7 +5075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>62</v>
       </c>
@@ -5164,95 +5167,95 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="9">
         <v>0.97289999999999999</v>
       </c>
-      <c r="C50" s="10">
-        <v>1</v>
-      </c>
-      <c r="D50" s="10">
+      <c r="C50" s="9">
+        <v>1</v>
+      </c>
+      <c r="D50" s="9">
         <v>0.82679999999999998</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="9">
         <v>0.91990000000000005</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="9">
         <v>0.86009999999999998</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="9">
         <v>0.83579999999999999</v>
       </c>
-      <c r="H50" s="10">
-        <v>1</v>
-      </c>
-      <c r="I50" s="10">
+      <c r="H50" s="9">
+        <v>1</v>
+      </c>
+      <c r="I50" s="9">
         <v>0.90600000000000003</v>
       </c>
-      <c r="J50" s="10">
-        <v>1</v>
-      </c>
-      <c r="K50" s="10">
+      <c r="J50" s="9">
+        <v>1</v>
+      </c>
+      <c r="K50" s="9">
         <v>0.95709999999999995</v>
       </c>
-      <c r="L50" s="10">
+      <c r="L50" s="9">
         <v>0.92579999999999996</v>
       </c>
-      <c r="M50" s="10">
-        <v>1</v>
-      </c>
-      <c r="O50" s="9" t="s">
+      <c r="M50" s="9">
+        <v>1</v>
+      </c>
+      <c r="O50" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="P50" s="10">
+      <c r="P50" s="9">
         <v>0.93859999999999999</v>
       </c>
-      <c r="Q50" s="10">
+      <c r="Q50" s="9">
         <v>0.97140000000000004</v>
       </c>
-      <c r="R50" s="10">
+      <c r="R50" s="9">
         <v>0.97050000000000003</v>
       </c>
-      <c r="S50" s="10">
-        <v>1</v>
-      </c>
-      <c r="T50" s="10">
+      <c r="S50" s="9">
+        <v>1</v>
+      </c>
+      <c r="T50" s="9">
         <v>0.93059999999999998</v>
       </c>
-      <c r="U50" s="10">
-        <v>1</v>
-      </c>
-      <c r="V50" s="10">
-        <v>1</v>
-      </c>
-      <c r="W50" s="10">
+      <c r="U50" s="9">
+        <v>1</v>
+      </c>
+      <c r="V50" s="9">
+        <v>1</v>
+      </c>
+      <c r="W50" s="9">
         <v>0.25850000000000001</v>
       </c>
-      <c r="X50" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y50" s="10">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="10">
+      <c r="X50" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="9">
         <v>0.48749999999999999</v>
       </c>
-      <c r="AA50" s="10">
+      <c r="AA50" s="9">
         <v>0.99539999999999995</v>
       </c>
-      <c r="AB50" s="10">
-        <v>1</v>
-      </c>
-      <c r="AC50" s="10">
+      <c r="AB50" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="9">
         <v>0.58579999999999999</v>
       </c>
-      <c r="AD50" s="10">
+      <c r="AD50" s="9">
         <v>0.53269999999999995</v>
       </c>
-      <c r="AE50" s="10">
+      <c r="AE50" s="9">
         <v>1</v>
       </c>
     </row>
